--- a/docs/sanctions_watch.xlsx
+++ b/docs/sanctions_watch.xlsx
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>EU; US</t>
+          <t>UN; EU; US</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5216,28 +5216,24 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Mediterranean Sea</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Russia -&gt; Ukraine</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
           <t>DF Peak</t>
@@ -5255,7 +5251,9 @@
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="n">
+        <v>700000</v>
+      </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="n">
@@ -5263,7 +5261,7 @@
       </c>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -5277,11 +5275,11 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>False, fraudulent or changed flag; Sanctioned person, company or vessel named; Intelligence-led find; Shell or front company; Price-cap breach; Vessel renamed or ownership changed; Re-export / transshipment via a third country</t>
+          <t>False, fraudulent or changed flag; Sanctioned person, company or vessel named; Intelligence-led find; Shell or front company; Price-cap breach; Vessel renamed or ownership changed; Re-export / transshipment via a third country; No valid insurance</t>
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
@@ -5290,7 +5288,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>The French Navy detained a sanctioned tanker from russia’s shadow fleet</t>
+          <t>French Navy Boards Sanctioned Russian Shadow Tanker DF Peak in Indian Ocean</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -7691,7 +7689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7992,12 +7990,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -8011,12 +8009,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8026,23 +8024,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Refined fuel / diesel / LNG</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -8071,7 +8069,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Refined fuel / diesel / LNG</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -8082,12 +8080,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -8101,12 +8099,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8119,20 +8117,24 @@
           <t>Vessel / tanker seized</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -8146,12 +8148,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8164,57 +8166,8 @@
           <t>Vessel / tanker seized</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Vessel / tanker seized</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8229,7 +8182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8379,12 +8332,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Gulf of Aden</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -8399,18 +8352,18 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gulf of Aden</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -8421,7 +8374,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Crude oil; Cryptocurrency</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -8431,23 +8384,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Crude oil; Cryptocurrency</t>
+          <t>Nuclear / missile-related items</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -8457,12 +8410,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -8473,7 +8426,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nuclear / missile-related items</t>
+          <t>Crude oil</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -8483,12 +8436,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -8499,7 +8452,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -8509,12 +8462,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -8525,7 +8478,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Crude oil</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -8535,12 +8488,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -8551,7 +8504,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -8561,12 +8514,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -8587,12 +8540,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>Anchorage</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -8613,12 +8566,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Anchorage</t>
+          <t>Prague</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -8639,12 +8592,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Prague</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -8665,12 +8618,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Mediterranean Sea</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -8691,12 +8644,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mediterranean Sea</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -8717,7 +8670,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8821,12 +8774,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Mediterranean Sea</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -8837,22 +8790,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Other sanctioned goods</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saint Petersburg</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -8863,7 +8816,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Other sanctioned goods</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -8873,12 +8826,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Port Everglades</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -8889,7 +8842,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Refined fuel / diesel / LNG</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -8899,12 +8852,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vladivostok</t>
+          <t>Port Everglades</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -8915,7 +8868,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Refined fuel / diesel / LNG</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -8925,12 +8878,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Vladivostok</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -8951,12 +8904,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -8967,7 +8920,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vehicles</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -8977,12 +8930,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gulf of Aden</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -8993,22 +8946,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Vehicles</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Gulf of Aden</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -9019,22 +8972,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mediterranean Sea</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -9045,7 +8998,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Crude oil</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -9055,26 +9008,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Mediterranean Sea</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Vessel / tanker seized</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>London</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>Vessel / tanker seized</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9595,7 +9574,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Mediterranean Sea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/docs/sanctions_watch.xlsx
+++ b/docs/sanctions_watch.xlsx
@@ -5110,60 +5110,70 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Baltic Sea</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>Trelleborg</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Equatorial Guinea</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Equatorial Guinea -&gt; Sweden</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>Sea Owl 1</t>
         </is>
       </c>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Comoros</t>
+        </is>
+      </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="n">
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>False, fraudulent or changed flag; Sanctioned person, company or vessel named; Flag registry often named in reports on fraudulent flags: Comoros</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>False, fraudulent or changed flag; Sanctioned person, company or vessel named</t>
+        </is>
+      </c>
+      <c r="AE50" t="n">
         <v>2</v>
       </c>
-      <c r="AA50" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>False, fraudulent or changed flag; Sanctioned person, company or vessel named</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>False, fraudulent or changed flag; Sanctioned person, company or vessel named</t>
-        </is>
-      </c>
-      <c r="AE50" t="n">
-        <v>1</v>
-      </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>The Maritime Executive</t>
+          <t>The Maritime Executive; Бабель</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>Sweden Releases Sanctioned Tanker After Seven-Month Detention</t>
+          <t>Sweden releases tanker under EU sanctions after it was detained in March</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -5231,7 +5241,11 @@
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
@@ -5261,7 +5275,7 @@
       </c>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -5279,7 +5293,7 @@
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
@@ -5975,7 +5989,11 @@
           <t>Russia / Ukraine-related</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>Coast guard / navy</t>
@@ -5998,7 +6016,11 @@
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>DF Peak</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6009,26 +6031,34 @@
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>False, fraudulent or changed flag; Shell or front company; Re-export / transshipment via a third country</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>False, fraudulent or changed flag; Shell or front company; Re-export / transshipment via a third country</t>
+        </is>
+      </c>
+      <c r="AE59" t="n">
         <v>4</v>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="n">
-        <v>3</v>
-      </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>USNI News; Yahoo News Canada; streamlinefeed.co.ke</t>
+          <t>USNI News; Yahoo News Canada; safety4sea; streamlinefeed.co.ke</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>French Navy intercepts suspected Russian shadow fleet tanker in Indian Ocean</t>
+          <t>French Navy boards suspected shadow fleet tanker in Indian Ocean</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
@@ -6286,7 +6316,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Refined fuel / diesel / LNG</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6307,15 +6337,19 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>Cuba</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
@@ -6358,16 +6392,16 @@
         </is>
       </c>
       <c r="AE62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>El Universal; Marine Insight</t>
+          <t>Baird Maritime; El Universal; Marine Insight</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>U.S Coast Guard Intercepts Cargo Ship Carrying Fuel Bound For Cuba Amid Oil Embargo</t>
+          <t>Cuba-bound ship carrying fuel seized by US Coast Guard as embargo bites</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
@@ -7689,7 +7723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7810,31 +7844,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7855,12 +7889,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -7874,12 +7908,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7990,12 +8024,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -8009,12 +8043,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8024,23 +8058,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Refined fuel / diesel / LNG</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -8069,7 +8103,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Refined fuel / diesel / LNG</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -8080,12 +8114,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -8099,12 +8133,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8117,24 +8151,20 @@
           <t>Vessel / tanker seized</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -8148,26 +8178,75 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Vessel / tanker seized</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>up</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Vessel / tanker seized</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8182,7 +8261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8332,12 +8411,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gulf of Aden</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -8358,12 +8437,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -8374,7 +8453,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Crude oil; Cryptocurrency</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -8384,23 +8463,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Gulf of Aden</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nuclear / missile-related items</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -8410,23 +8489,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Crude oil; Cryptocurrency</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -8436,12 +8515,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -8452,7 +8531,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Nuclear / missile-related items</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -8462,12 +8541,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -8488,12 +8567,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -8504,7 +8583,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Crude oil</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -8748,12 +8827,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Baltic Sea</t>
+          <t>Mediterranean Sea</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -8768,18 +8847,18 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mediterranean Sea</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -8790,22 +8869,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Other sanctioned goods</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -8816,7 +8895,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Other sanctioned goods</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -8826,12 +8905,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Saint Petersburg</t>
+          <t>Port Everglades</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -8842,7 +8921,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Refined fuel / diesel / LNG</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -8852,12 +8931,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Port Everglades</t>
+          <t>Vladivostok</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -8868,7 +8947,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Refined fuel / diesel / LNG</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -8878,12 +8957,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vladivostok</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -8894,7 +8973,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Vehicles</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -8904,12 +8983,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Gulf of Aden</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -8924,18 +9003,18 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -8946,7 +9025,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vehicles</t>
+          <t>Crude oil</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -8956,12 +9035,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gulf of Aden</t>
+          <t>Mediterranean Sea</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -8976,18 +9055,18 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>London</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -8998,62 +9077,10 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Mediterranean Sea</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Vessel / tanker seized</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Vessel / tanker seized</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9068,7 +9095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9443,12 +9470,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Refined fuel / diesel / LNG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9505,12 +9532,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sea Owl 1</t>
+          <t>DF Peak</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sea Owl 1</t>
+          <t>DF Peak</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -9519,22 +9546,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Baltic Sea</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fertiliser / grain / food</t>
+          <t>Crude oil</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9546,17 +9573,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IMO 9341067</t>
+          <t>Sea Owl 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DF Peak</t>
+          <t>Sea Owl 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -9574,12 +9601,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mediterranean Sea</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Fertiliser / grain / food</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9591,17 +9618,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Caffa</t>
+          <t>IMO 9341067</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caffa</t>
+          <t>DF Peak</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -9609,22 +9636,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Mediterranean Sea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fertiliser / grain / food</t>
+          <t>Crude oil</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9636,17 +9663,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Linked</t>
+          <t>Caffa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Linked</t>
+          <t>Caffa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -9664,12 +9691,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kaliningrad</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Fertiliser / grain / food</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9681,15 +9708,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Linked</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>French</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
@@ -9705,7 +9736,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Kaliningrad</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9722,12 +9753,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ethera</t>
+          <t>French</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ethera</t>
+          <t>French</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -9746,10 +9777,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anchorage</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Russia / Ukraine-related</t>
@@ -9759,12 +9794,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Ethera</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Ethera</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -9783,14 +9818,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Crude oil</t>
-        </is>
-      </c>
+          <t>Anchorage</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Russia / Ukraine-related</t>
@@ -9800,12 +9831,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vautrin</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vautrin</t>
+          <t>News</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -9829,7 +9860,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Refined fuel / diesel / LNG</t>
+          <t>Crude oil</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9841,12 +9872,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tra</t>
+          <t>Vautrin</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tra</t>
+          <t>Vautrin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -9865,12 +9896,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kaliningrad</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Refined fuel / diesel / LNG</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9882,12 +9913,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>Tra</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>Tra</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -9906,7 +9937,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Kaliningrad</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -9923,43 +9954,84 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>SUN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SUN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Russia / Ukraine-related</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Tied</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Tied</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Moscow</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Refined fuel / diesel / LNG</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Russia / Ukraine-related</t>
         </is>

--- a/docs/sanctions_watch.xlsx
+++ b/docs/sanctions_watch.xlsx
@@ -19307,7 +19307,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -20221,7 +20221,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>

--- a/docs/sanctions_watch.xlsx
+++ b/docs/sanctions_watch.xlsx
@@ -19151,10 +19151,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -19200,10 +19200,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -20417,23 +20417,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gulf of Aden</t>
+          <t>Mediterranean Sea</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized</t>
+          <t>Vessel / tanker seized; Crude oil</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -20443,12 +20443,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mediterranean Sea</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -20459,7 +20459,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized; Crude oil</t>
+          <t>Vessel / tanker seized; Other sanctioned goods</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -20469,23 +20469,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Gulf of Aden</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vessel / tanker seized; Other sanctioned goods</t>
+          <t>Vessel / tanker seized</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -20637,7 +20637,7 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>

--- a/docs/sanctions_watch.xlsx
+++ b/docs/sanctions_watch.xlsx
@@ -21867,7 +21867,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -26756,12 +26756,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Unspecified: 6 seizure reports in the last 7 days</t>
+          <t>Unspecified: 5 seizure reports in the last 7 days</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8-week average 0.5</t>
+          <t>8-week average 0.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>

--- a/docs/sanctions_watch.xlsx
+++ b/docs/sanctions_watch.xlsx
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ABC27</t>
+          <t>ABC27; Agenzia Nova</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="AE64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
